--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_IBERSOL CB TARRAGONA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_IBERSOL CB TARRAGONA.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. BUSCAIL BRIANSO</t>
+          <t>D. FERNANDEZ STEFANUTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,76 +562,76 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>98.66589999999999</v>
+        <v>108.767</v>
       </c>
       <c r="E2" t="n">
-        <v>49.5164</v>
+        <v>75.4667</v>
       </c>
       <c r="F2" t="n">
-        <v>49.1492</v>
+        <v>33.3002</v>
       </c>
       <c r="G2" t="n">
-        <v>31.6571</v>
+        <v>48.6632</v>
       </c>
       <c r="H2" t="n">
-        <v>24.0048</v>
+        <v>31.6411</v>
       </c>
       <c r="I2" t="n">
-        <v>7.6525</v>
+        <v>17.022</v>
       </c>
       <c r="J2" t="n">
-        <v>39.1995</v>
+        <v>68.5604</v>
       </c>
       <c r="K2" t="n">
-        <v>27.0476</v>
+        <v>44.5388</v>
       </c>
       <c r="L2" t="n">
-        <v>12.1517</v>
+        <v>24.0219</v>
       </c>
       <c r="M2" t="n">
-        <v>-7.5424</v>
+        <v>-19.8973</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.0429</v>
+        <v>-12.8975</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.4993</v>
+        <v>-6.9996</v>
       </c>
       <c r="P2" t="n">
-        <v>5.5546</v>
+        <v>3.174</v>
       </c>
       <c r="Q2" t="n">
-        <v>-49.7943</v>
+        <v>-56.14239999999999</v>
       </c>
       <c r="R2" t="n">
-        <v>55.3491</v>
+        <v>59.3168</v>
       </c>
       <c r="S2" t="n">
-        <v>44.219</v>
+        <v>15.5546</v>
       </c>
       <c r="T2" t="n">
-        <v>26.6208</v>
+        <v>5.9942</v>
       </c>
       <c r="U2" t="n">
-        <v>17.5984</v>
+        <v>9.5604</v>
       </c>
       <c r="V2" t="n">
-        <v>17.2349</v>
+        <v>41.375</v>
       </c>
       <c r="W2" t="n">
-        <v>33.4907</v>
+        <v>57.0549</v>
       </c>
       <c r="X2" t="n">
-        <v>-16.2558</v>
+        <v>-15.6796</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ STEFANUTO</t>
+          <t>M. BUSCAIL BRIANSO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>88.8663</v>
+        <v>80.35850000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>60.5761</v>
+        <v>35.8218</v>
       </c>
       <c r="F3" t="n">
-        <v>28.2898</v>
+        <v>44.5367</v>
       </c>
       <c r="G3" t="n">
-        <v>48.6632</v>
+        <v>31.6571</v>
       </c>
       <c r="H3" t="n">
-        <v>31.6411</v>
+        <v>24.0048</v>
       </c>
       <c r="I3" t="n">
-        <v>17.022</v>
+        <v>7.6525</v>
       </c>
       <c r="J3" t="n">
-        <v>68.5604</v>
+        <v>39.1995</v>
       </c>
       <c r="K3" t="n">
-        <v>44.5388</v>
+        <v>27.0476</v>
       </c>
       <c r="L3" t="n">
-        <v>24.0219</v>
+        <v>12.1517</v>
       </c>
       <c r="M3" t="n">
-        <v>-19.8973</v>
+        <v>-7.5424</v>
       </c>
       <c r="N3" t="n">
-        <v>-12.8975</v>
+        <v>-3.0429</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.9996</v>
+        <v>-4.4993</v>
       </c>
       <c r="P3" t="n">
-        <v>3.174</v>
+        <v>5.5546</v>
       </c>
       <c r="Q3" t="n">
-        <v>-56.14239999999999</v>
+        <v>-49.7943</v>
       </c>
       <c r="R3" t="n">
-        <v>59.3168</v>
+        <v>55.3491</v>
       </c>
       <c r="S3" t="n">
-        <v>-4.3459</v>
+        <v>25.9115</v>
       </c>
       <c r="T3" t="n">
-        <v>-8.896699999999999</v>
+        <v>12.9262</v>
       </c>
       <c r="U3" t="n">
-        <v>4.5504</v>
+        <v>12.9851</v>
       </c>
       <c r="V3" t="n">
-        <v>41.375</v>
+        <v>17.2349</v>
       </c>
       <c r="W3" t="n">
-        <v>57.0549</v>
+        <v>33.4907</v>
       </c>
       <c r="X3" t="n">
-        <v>-15.6796</v>
+        <v>-16.2558</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>26</v>
       </c>
       <c r="D4" t="n">
-        <v>73.3896</v>
+        <v>46.9594</v>
       </c>
       <c r="E4" t="n">
-        <v>30.4654</v>
+        <v>13.3808</v>
       </c>
       <c r="F4" t="n">
-        <v>42.9241</v>
+        <v>33.5786</v>
       </c>
       <c r="G4" t="n">
         <v>20.4716</v>
@@ -766,13 +766,13 @@
         <v>57.1347</v>
       </c>
       <c r="S4" t="n">
-        <v>57.5235</v>
+        <v>31.0935</v>
       </c>
       <c r="T4" t="n">
-        <v>31.5809</v>
+        <v>14.4964</v>
       </c>
       <c r="U4" t="n">
-        <v>25.9428</v>
+        <v>16.5971</v>
       </c>
       <c r="V4" t="n">
         <v>-1.8281</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. SENGHOR</t>
+          <t>A. DUCH BELTRAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D5" t="n">
-        <v>22.2432</v>
+        <v>30.8114</v>
       </c>
       <c r="E5" t="n">
-        <v>20.1484</v>
+        <v>23.0263</v>
       </c>
       <c r="F5" t="n">
-        <v>2.0951</v>
+        <v>7.784800000000001</v>
       </c>
       <c r="G5" t="n">
-        <v>8.3643</v>
+        <v>15.2717</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9604999999999999</v>
+        <v>6.5388</v>
       </c>
       <c r="I5" t="n">
-        <v>9.325099999999999</v>
+        <v>8.732799999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>22.0914</v>
+        <v>22.6089</v>
       </c>
       <c r="K5" t="n">
-        <v>7.617599999999999</v>
+        <v>11.3903</v>
       </c>
       <c r="L5" t="n">
-        <v>14.4734</v>
+        <v>11.2185</v>
       </c>
       <c r="M5" t="n">
-        <v>-13.7265</v>
+        <v>-7.3368</v>
       </c>
       <c r="N5" t="n">
-        <v>-8.5779</v>
+        <v>-4.8513</v>
       </c>
       <c r="O5" t="n">
-        <v>-5.1486</v>
+        <v>-2.4857</v>
       </c>
       <c r="P5" t="n">
-        <v>9.1258</v>
+        <v>10.1179</v>
       </c>
       <c r="Q5" t="n">
-        <v>-17.2591</v>
+        <v>-21.4253</v>
       </c>
       <c r="R5" t="n">
-        <v>26.3855</v>
+        <v>31.5432</v>
       </c>
       <c r="S5" t="n">
-        <v>4.9638</v>
+        <v>-2.2603</v>
       </c>
       <c r="T5" t="n">
-        <v>6.287599999999999</v>
+        <v>-0.1913</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.3238</v>
+        <v>-2.0691</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2106000000000001</v>
+        <v>7.6825</v>
       </c>
       <c r="W5" t="n">
-        <v>9.0297</v>
+        <v>22.0344</v>
       </c>
       <c r="X5" t="n">
-        <v>-9.2402</v>
+        <v>-14.352</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HALL</t>
+          <t>D. FERNANDEZ LINARES</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>19.8462</v>
+        <v>30.4785</v>
       </c>
       <c r="E6" t="n">
-        <v>21.0223</v>
+        <v>5.4621</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.1762</v>
+        <v>25.0166</v>
       </c>
       <c r="G6" t="n">
-        <v>9.9559</v>
+        <v>2.2248</v>
       </c>
       <c r="H6" t="n">
-        <v>4.6827</v>
+        <v>4.295800000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>5.273</v>
+        <v>-2.0708</v>
       </c>
       <c r="J6" t="n">
-        <v>15.563</v>
+        <v>20.7563</v>
       </c>
       <c r="K6" t="n">
-        <v>9.448399999999999</v>
+        <v>14.4926</v>
       </c>
       <c r="L6" t="n">
-        <v>6.1148</v>
+        <v>6.2636</v>
       </c>
       <c r="M6" t="n">
-        <v>-5.6073</v>
+        <v>-18.5317</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.7655</v>
+        <v>-10.1974</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8417000000000001</v>
+        <v>-8.334300000000001</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9919999999999999</v>
+        <v>3.1742</v>
       </c>
       <c r="Q6" t="n">
-        <v>-6.5466</v>
+        <v>-45.033</v>
       </c>
       <c r="R6" t="n">
-        <v>7.5387</v>
+        <v>48.2075</v>
       </c>
       <c r="S6" t="n">
-        <v>12.2908</v>
+        <v>11.372</v>
       </c>
       <c r="T6" t="n">
-        <v>9.398299999999999</v>
+        <v>6.498</v>
       </c>
       <c r="U6" t="n">
-        <v>2.8926</v>
+        <v>4.8736</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.3924</v>
+        <v>13.7084</v>
       </c>
       <c r="W6" t="n">
-        <v>2.6076</v>
+        <v>23.2411</v>
       </c>
       <c r="X6" t="n">
-        <v>-6.000000000000001</v>
+        <v>-9.5326</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. FERNANDEZ LINARES</t>
+          <t>A. SENGHOR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>12.6933</v>
+        <v>22.5778</v>
       </c>
       <c r="E7" t="n">
-        <v>-6.775700000000001</v>
+        <v>18.7257</v>
       </c>
       <c r="F7" t="n">
-        <v>19.4691</v>
+        <v>3.8523</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2248</v>
+        <v>8.3643</v>
       </c>
       <c r="H7" t="n">
-        <v>4.295800000000001</v>
+        <v>-0.9604999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0708</v>
+        <v>9.325099999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>20.7563</v>
+        <v>22.0914</v>
       </c>
       <c r="K7" t="n">
-        <v>14.4926</v>
+        <v>7.617599999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>6.2636</v>
+        <v>14.4734</v>
       </c>
       <c r="M7" t="n">
-        <v>-18.5317</v>
+        <v>-13.7265</v>
       </c>
       <c r="N7" t="n">
-        <v>-10.1974</v>
+        <v>-8.5779</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.334300000000001</v>
+        <v>-5.1486</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1742</v>
+        <v>9.1258</v>
       </c>
       <c r="Q7" t="n">
-        <v>-45.033</v>
+        <v>-17.2591</v>
       </c>
       <c r="R7" t="n">
-        <v>48.2075</v>
+        <v>26.3855</v>
       </c>
       <c r="S7" t="n">
-        <v>-6.413600000000001</v>
+        <v>5.2979</v>
       </c>
       <c r="T7" t="n">
-        <v>-5.7398</v>
+        <v>4.8648</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.6741</v>
+        <v>0.4337999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>13.7084</v>
+        <v>-0.2106000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>23.2411</v>
+        <v>9.0297</v>
       </c>
       <c r="X7" t="n">
-        <v>-9.5326</v>
+        <v>-9.2402</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. DUCH BELTRAN</t>
+          <t>S. HALL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,70 +1030,70 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>10.911</v>
+        <v>14.3514</v>
       </c>
       <c r="E8" t="n">
-        <v>10.5507</v>
+        <v>16.2893</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3602999999999997</v>
+        <v>-1.9379</v>
       </c>
       <c r="G8" t="n">
-        <v>15.2717</v>
+        <v>9.9559</v>
       </c>
       <c r="H8" t="n">
-        <v>6.5388</v>
+        <v>4.6827</v>
       </c>
       <c r="I8" t="n">
-        <v>8.732799999999999</v>
+        <v>5.273</v>
       </c>
       <c r="J8" t="n">
-        <v>22.6089</v>
+        <v>15.563</v>
       </c>
       <c r="K8" t="n">
-        <v>11.3903</v>
+        <v>9.448399999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>11.2185</v>
+        <v>6.1148</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.3368</v>
+        <v>-5.6073</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.8513</v>
+        <v>-4.7655</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4857</v>
+        <v>-0.8417000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>10.1179</v>
+        <v>0.9919999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-21.4253</v>
+        <v>-6.5466</v>
       </c>
       <c r="R8" t="n">
-        <v>31.5432</v>
+        <v>7.5387</v>
       </c>
       <c r="S8" t="n">
-        <v>-22.1605</v>
+        <v>6.796</v>
       </c>
       <c r="T8" t="n">
-        <v>-12.667</v>
+        <v>4.6654</v>
       </c>
       <c r="U8" t="n">
-        <v>-9.4939</v>
+        <v>2.1308</v>
       </c>
       <c r="V8" t="n">
-        <v>7.6825</v>
+        <v>-3.3924</v>
       </c>
       <c r="W8" t="n">
-        <v>22.0344</v>
+        <v>2.6076</v>
       </c>
       <c r="X8" t="n">
-        <v>-14.352</v>
+        <v>-6.000000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>26</v>
       </c>
       <c r="D9" t="n">
-        <v>8.733899999999998</v>
+        <v>14.3258</v>
       </c>
       <c r="E9" t="n">
-        <v>-5.8549</v>
+        <v>-3.3953</v>
       </c>
       <c r="F9" t="n">
-        <v>14.5888</v>
+        <v>17.7208</v>
       </c>
       <c r="G9" t="n">
         <v>27.6496</v>
@@ -1156,13 +1156,13 @@
         <v>32.9319</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5835</v>
+        <v>7.1756</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3756999999999999</v>
+        <v>2.835599999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2078</v>
+        <v>4.3401</v>
       </c>
       <c r="V9" t="n">
         <v>-11.374</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ISSOUF</t>
+          <t>I. FERNANDEZ MASIP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1186,76 +1186,76 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D10" t="n">
-        <v>8.652700000000001</v>
+        <v>13.9153</v>
       </c>
       <c r="E10" t="n">
-        <v>5.9647</v>
+        <v>3.611599999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>2.6878</v>
+        <v>10.3037</v>
       </c>
       <c r="G10" t="n">
-        <v>4.4531</v>
+        <v>16.3613</v>
       </c>
       <c r="H10" t="n">
-        <v>5.0656</v>
+        <v>6.3591</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.6126</v>
+        <v>10.0021</v>
       </c>
       <c r="J10" t="n">
-        <v>7.4725</v>
+        <v>36.7777</v>
       </c>
       <c r="K10" t="n">
-        <v>6.1875</v>
+        <v>18.9854</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2852</v>
+        <v>17.7926</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0193</v>
+        <v>-20.4167</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.1217</v>
+        <v>-12.6263</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.8977</v>
+        <v>-7.7904</v>
       </c>
       <c r="P10" t="n">
-        <v>-6.745100000000001</v>
+        <v>-8.3322</v>
       </c>
       <c r="Q10" t="n">
-        <v>-12.1014</v>
+        <v>-57.333</v>
       </c>
       <c r="R10" t="n">
-        <v>5.3564</v>
+        <v>49.0009</v>
       </c>
       <c r="S10" t="n">
-        <v>9.134699999999999</v>
+        <v>14.248</v>
       </c>
       <c r="T10" t="n">
-        <v>7.4542</v>
+        <v>8.754200000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>1.6808</v>
+        <v>5.4943</v>
       </c>
       <c r="V10" t="n">
-        <v>1.8097</v>
+        <v>-8.361599999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>3.1397</v>
+        <v>15.413</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.3299</v>
+        <v>-23.775</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>I. FERNANDEZ MASIP</t>
+          <t>T. KOHAN LÓPEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
-        <v>6.934</v>
+        <v>9.4459</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7073999999999991</v>
+        <v>5.555099999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>7.641399999999999</v>
+        <v>3.8907</v>
       </c>
       <c r="G11" t="n">
-        <v>16.3613</v>
+        <v>3.8228</v>
       </c>
       <c r="H11" t="n">
-        <v>6.3591</v>
+        <v>2.1436</v>
       </c>
       <c r="I11" t="n">
-        <v>10.0021</v>
+        <v>1.6793</v>
       </c>
       <c r="J11" t="n">
-        <v>36.7777</v>
+        <v>9.8062</v>
       </c>
       <c r="K11" t="n">
-        <v>18.9854</v>
+        <v>4.6425</v>
       </c>
       <c r="L11" t="n">
-        <v>17.7926</v>
+        <v>5.1637</v>
       </c>
       <c r="M11" t="n">
-        <v>-20.4167</v>
+        <v>-5.9834</v>
       </c>
       <c r="N11" t="n">
-        <v>-12.6263</v>
+        <v>-2.498699999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.7904</v>
+        <v>-3.4846</v>
       </c>
       <c r="P11" t="n">
-        <v>-8.3322</v>
+        <v>4.166</v>
       </c>
       <c r="Q11" t="n">
-        <v>-57.333</v>
+        <v>-5.5547</v>
       </c>
       <c r="R11" t="n">
-        <v>49.0009</v>
+        <v>9.7209</v>
       </c>
       <c r="S11" t="n">
-        <v>7.267</v>
+        <v>1.6623</v>
       </c>
       <c r="T11" t="n">
-        <v>4.4348</v>
+        <v>1.0378</v>
       </c>
       <c r="U11" t="n">
-        <v>2.8322</v>
+        <v>0.6242999999999999</v>
       </c>
       <c r="V11" t="n">
-        <v>-8.361599999999999</v>
+        <v>-0.205</v>
       </c>
       <c r="W11" t="n">
-        <v>15.413</v>
+        <v>0.266</v>
       </c>
       <c r="X11" t="n">
-        <v>-23.775</v>
+        <v>-0.471</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. KOHAN LÓPEZ</t>
+          <t>M. ISSOUF</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,70 +1342,70 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5932</v>
+        <v>3.4968</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3492</v>
+        <v>1.458600000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2439</v>
+        <v>2.0383</v>
       </c>
       <c r="G12" t="n">
-        <v>3.8228</v>
+        <v>4.4531</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1436</v>
+        <v>5.0656</v>
       </c>
       <c r="I12" t="n">
-        <v>1.6793</v>
+        <v>-0.6126</v>
       </c>
       <c r="J12" t="n">
-        <v>9.8062</v>
+        <v>7.4725</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6425</v>
+        <v>6.1875</v>
       </c>
       <c r="L12" t="n">
-        <v>5.1637</v>
+        <v>1.2852</v>
       </c>
       <c r="M12" t="n">
-        <v>-5.9834</v>
+        <v>-3.0193</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.498699999999999</v>
+        <v>-1.1217</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.4846</v>
+        <v>-1.8977</v>
       </c>
       <c r="P12" t="n">
-        <v>4.166</v>
+        <v>-6.745100000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>-5.5547</v>
+        <v>-12.1014</v>
       </c>
       <c r="R12" t="n">
-        <v>9.7209</v>
+        <v>5.3564</v>
       </c>
       <c r="S12" t="n">
-        <v>-4.1906</v>
+        <v>3.979</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.1683</v>
+        <v>2.9479</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.0222</v>
+        <v>1.0311</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.205</v>
+        <v>1.8097</v>
       </c>
       <c r="W12" t="n">
-        <v>0.266</v>
+        <v>3.1397</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.471</v>
+        <v>-1.3299</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>6</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9268000000000001</v>
+        <v>1.9663</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.01600000000000007</v>
+        <v>0.4148000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9425999999999999</v>
+        <v>1.5513</v>
       </c>
       <c r="G13" t="n">
         <v>5.1668</v>
@@ -1468,13 +1468,13 @@
         <v>3.3726</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.2753</v>
+        <v>-1.2358</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9408</v>
+        <v>-0.51</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3346</v>
+        <v>-0.7259</v>
       </c>
       <c r="V13" t="n">
         <v>-3.3535</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MESA RUIZ</t>
+          <t>A. BLÁZQUEZ FARRIOL</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5238</v>
+        <v>0.9248000000000004</v>
       </c>
       <c r="E14" t="n">
-        <v>2.275</v>
+        <v>-1.0239</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.7512</v>
+        <v>1.9488</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3646</v>
+        <v>-2.9435</v>
       </c>
       <c r="H14" t="n">
-        <v>1.5877</v>
+        <v>1.001</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.9524</v>
+        <v>-3.9446</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5533</v>
+        <v>2.9092</v>
       </c>
       <c r="K14" t="n">
-        <v>2.5106</v>
+        <v>5.5719</v>
       </c>
       <c r="L14" t="n">
-        <v>0.04269999999999996</v>
+        <v>-2.662700000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.918</v>
+        <v>-5.853</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9228999999999999</v>
+        <v>-4.5708</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.9951</v>
+        <v>-1.282</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.595</v>
+        <v>6.1501</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9838</v>
+        <v>-7.1418</v>
       </c>
       <c r="R14" t="n">
-        <v>1.3888</v>
+        <v>13.2922</v>
       </c>
       <c r="S14" t="n">
-        <v>1.8921</v>
+        <v>1.7841</v>
       </c>
       <c r="T14" t="n">
-        <v>1.848</v>
+        <v>2.9425</v>
       </c>
       <c r="U14" t="n">
-        <v>0.04409999999999996</v>
+        <v>-1.1583</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.4085</v>
+        <v>-4.066</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.1425</v>
+        <v>0.266</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.266</v>
+        <v>-4.3319</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. BLÁZQUEZ FARRIOL</t>
+          <t>A. MESA RUIZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.3930000000000002</v>
+        <v>-0.2687</v>
       </c>
       <c r="E15" t="n">
-        <v>1.317</v>
+        <v>1.4588</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9237999999999997</v>
+        <v>-1.7274</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.9435</v>
+        <v>-0.3646</v>
       </c>
       <c r="H15" t="n">
-        <v>1.001</v>
+        <v>1.5877</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.9446</v>
+        <v>-1.9524</v>
       </c>
       <c r="J15" t="n">
-        <v>2.9092</v>
+        <v>2.5533</v>
       </c>
       <c r="K15" t="n">
-        <v>5.5719</v>
+        <v>2.5106</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.662700000000001</v>
+        <v>0.04269999999999996</v>
       </c>
       <c r="M15" t="n">
-        <v>-5.853</v>
+        <v>-2.918</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.5708</v>
+        <v>-0.9228999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.282</v>
+        <v>-1.9951</v>
       </c>
       <c r="P15" t="n">
-        <v>6.1501</v>
+        <v>-0.595</v>
       </c>
       <c r="Q15" t="n">
-        <v>-7.1418</v>
+        <v>-1.9838</v>
       </c>
       <c r="R15" t="n">
-        <v>13.2922</v>
+        <v>1.3888</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2524</v>
+        <v>1.0997</v>
       </c>
       <c r="T15" t="n">
-        <v>5.2836</v>
+        <v>1.0317</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.0311</v>
+        <v>0.0679</v>
       </c>
       <c r="V15" t="n">
-        <v>-4.066</v>
+        <v>-0.4085</v>
       </c>
       <c r="W15" t="n">
-        <v>0.266</v>
+        <v>-0.1425</v>
       </c>
       <c r="X15" t="n">
-        <v>-4.3319</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>6</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6403</v>
+        <v>-1.4005</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.5602</v>
+        <v>-0.1519999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.08</v>
+        <v>-1.2484</v>
       </c>
       <c r="G16" t="n">
         <v>-1.0598</v>
@@ -1702,13 +1702,13 @@
         <v>1.9839</v>
       </c>
       <c r="S16" t="n">
-        <v>1.1064</v>
+        <v>1.3462</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3176</v>
+        <v>0.7256</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7888999999999999</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>-2.6789</v>
@@ -1735,13 +1735,13 @@
         <v>20</v>
       </c>
       <c r="D17" t="n">
-        <v>-8.0366</v>
+        <v>-7.5121</v>
       </c>
       <c r="E17" t="n">
-        <v>-5.725899999999999</v>
+        <v>-5.6976</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3108</v>
+        <v>-1.8141</v>
       </c>
       <c r="G17" t="n">
         <v>-6.6694</v>
@@ -1780,13 +1780,13 @@
         <v>10.1178</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1214</v>
+        <v>0.6462999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3280000000000001</v>
+        <v>-0.2999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4496000000000001</v>
+        <v>0.9461000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>-5.0594</v>
@@ -1813,13 +1813,13 @@
         <v>26</v>
       </c>
       <c r="D18" t="n">
-        <v>346.696</v>
+        <v>369.1976</v>
       </c>
       <c r="E18" t="n">
-        <v>183.5451</v>
+        <v>190.4028</v>
       </c>
       <c r="F18" t="n">
-        <v>163.1501</v>
+        <v>178.795</v>
       </c>
       <c r="G18" t="n">
         <v>183.0249</v>
@@ -1858,13 +1858,13 @@
         <v>412.6409</v>
       </c>
       <c r="S18" t="n">
-        <v>101.9687</v>
+        <v>124.4706</v>
       </c>
       <c r="T18" t="n">
-        <v>61.8609</v>
+        <v>68.7191</v>
       </c>
       <c r="U18" t="n">
-        <v>40.10789999999999</v>
+        <v>55.7518</v>
       </c>
       <c r="V18" t="n">
         <v>40.8725</v>
